--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.2</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,61 +3396,61 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>27</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2.25</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.16</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>27</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>1.16</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>6.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>27</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.16</v>
+        <v>1.88</v>
       </c>
       <c r="M25" t="n">
-        <v>6.7</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>27</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>27</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,61 +3515,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.4</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.2</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.16</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>27</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="M24" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="N24" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="N24" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,61 +3515,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>27</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.25</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.2</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,61 +3991,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.4</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,55 +2801,55 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2.2</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="N21" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,61 +3515,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>27</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.25</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="M30" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>27</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,61 +3277,61 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.25</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.16</v>
+        <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="N21" t="n">
-        <v>27</v>
+        <v>1.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>1.16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>6.7</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>27</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,61 +3753,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.4</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.2</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>3.13</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,61 +2920,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.4</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>6.7</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>27</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="M21" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,61 +3158,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.35</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.16</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>27</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M30" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.13</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.85</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.34</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3.13</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,61 +3515,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.35</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>27</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.16</v>
+        <v>2.35</v>
       </c>
       <c r="M27" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>27</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46001.41666666666</v>
+        <v>46001.375</v>
       </c>
     </row>
     <row r="3">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46001.44791666666</v>
+        <v>46001.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46001.44791666666</v>
+        <v>46001.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46001.54166666666</v>
+        <v>46001.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46001.54166666666</v>
+        <v>46001.44791666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46001.54166666666</v>
+        <v>46001.44791666666</v>
       </c>
     </row>
     <row r="9">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46001.54166666666</v>
+        <v>46001.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46001.54166666666</v>
+        <v>46001.5</v>
       </c>
     </row>
     <row r="11">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>27</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,61 +3991,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.25</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,61 +3158,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.35</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,61 +3396,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>1.4</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB25" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="M25" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>6.7</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.73</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.4</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="N20" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.16</v>
+        <v>2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>6.7</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>27</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,61 +3515,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>27</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.25</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,61 +3991,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>27</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB30" t="n">
         <v>2.25</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.78</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M25" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>27</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>6.7</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>27</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,55 +2682,55 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.2</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.88</v>
+        <v>1.16</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>6.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>27</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.35</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>27</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>1.16</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="N30" t="n">
-        <v>1.4</v>
+        <v>27</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>4.09</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>2.26</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>3.13</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.13</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,61 +3277,61 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.35</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,61 +3634,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.4</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.13</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>1.16</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>6.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>9</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>6.7</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2111,49 +2111,49 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46001.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.16</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>6.7</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>27</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.73</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>6.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>27</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.45</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>5.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>1.16</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="N29" t="n">
-        <v>2.92</v>
+        <v>27</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>5.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.45</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
         <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.07</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>27</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,61 +3634,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.4</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>27</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M30" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.76</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.57</v>
+        <v>5.93</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="W11" t="n">
         <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA11" t="n">
         <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
         <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
         <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.45</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>5.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.2</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>1.16</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2.92</v>
+        <v>27</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.76</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.57</v>
+        <v>5.93</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="N8" t="n">
-        <v>5.93</v>
+        <v>2.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>5.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.45</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
         <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.53</v>
+        <v>1.76</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2215,40 +2215,40 @@
         <v>3.13</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA15" t="n">
         <v>2.2</v>
@@ -2257,22 +2257,22 @@
         <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,49 +2325,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA16" t="n">
         <v>1.83</v>
@@ -2376,22 +2376,22 @@
         <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3524,40 +3524,40 @@
         <v>1.4</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA26" t="n">
         <v>1.53</v>
@@ -3572,16 +3572,16 @@
         <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z29" t="n">
         <v>3.95</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>27</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.55</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
         <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.53</v>
+        <v>1.76</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>5.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="W13" t="n">
         <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.76</v>
+        <v>2.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.08</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.52</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.54</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="O16" t="n">
-        <v>2.21</v>
+        <v>3.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.57</v>
+        <v>4.08</v>
       </c>
       <c r="R16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.19</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.55</v>
+        <v>3.68</v>
       </c>
       <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.34</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V17" t="n">
-        <v>6.05</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.83</v>
+        <v>3.74</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.25</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="T18" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.47</v>
+        <v>2.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.68</v>
+        <v>5.57</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="T19" t="n">
-        <v>3.09</v>
+        <v>2.73</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AF19" t="n">
         <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3.44</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>5.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.86</v>
+        <v>2.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="T22" t="n">
-        <v>1.99</v>
+        <v>2.29</v>
       </c>
       <c r="U22" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3.56</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
-        <v>2.97</v>
+        <v>5.98</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>2.16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>3.32</v>
       </c>
       <c r="P26" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.78</v>
+        <v>3.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>1.16</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>6.7</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>27</v>
       </c>
       <c r="O27" t="n">
-        <v>5.98</v>
+        <v>1.61</v>
       </c>
       <c r="P27" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.16</v>
+        <v>9.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.84</v>
+        <v>4.9</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>4.42</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.02</v>
+        <v>3.66</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>5.57</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.73</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.77</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="AA15" t="n">
         <v>1.83</v>
@@ -2257,22 +2257,22 @@
         <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.52</v>
+        <v>2.19</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.08</v>
+        <v>3.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.61</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.68</v>
+        <v>4.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
         <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.44</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>5.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.86</v>
+        <v>2.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.57</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
         <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="AA19" t="n">
         <v>1.83</v>
@@ -2733,22 +2733,22 @@
         <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.19</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>3.44</v>
       </c>
       <c r="P20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.83</v>
+        <v>3.86</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.21</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
-        <v>1.65</v>
+        <v>2.97</v>
       </c>
       <c r="P21" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="U21" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="V21" t="n">
-        <v>3.8</v>
+        <v>6.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>3.24</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.56</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>3.32</v>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>3.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.32</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.02</v>
+        <v>1.78</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="T26" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.97</v>
+        <v>1.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.66</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.82</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="V29" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.24</v>
+        <v>1.97</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>3.56</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.76</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.57</v>
+        <v>5.93</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1739,40 +1739,40 @@
         <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
         <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.55</v>
@@ -1787,7 +1787,7 @@
         <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AF11" t="n">
         <v>2.4</v>
@@ -1858,13 +1858,13 @@
         <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="P12" t="n">
         <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -1888,10 +1888,10 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
         <v>1.85</v>
@@ -1906,16 +1906,16 @@
         <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AF12" t="n">
         <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1977,19 +1977,19 @@
         <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="P13" t="n">
         <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.55</v>
+        <v>6.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
         <v>2.39</v>
@@ -2001,7 +2001,7 @@
         <v>5.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
@@ -2025,16 +2025,16 @@
         <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
         <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O15" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.57</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.52</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
         <v>1.83</v>
@@ -2257,22 +2257,22 @@
         <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.17</v>
+        <v>2.19</v>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.08</v>
+        <v>5.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>3.09</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.61</v>
+        <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.25</v>
+        <v>3.07</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>3.06</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.55</v>
+        <v>3.66</v>
       </c>
       <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.34</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V18" t="n">
-        <v>6.05</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AG18" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.07</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>5.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="T19" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.05</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.52</v>
+        <v>2.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,49 +2801,49 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="O20" t="n">
-        <v>3.44</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>4.13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="AA20" t="n">
         <v>2.2</v>
@@ -2852,22 +2852,22 @@
         <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.86</v>
+        <v>4.63</v>
       </c>
       <c r="AD20" t="n">
         <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,49 +3039,49 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
-        <v>3.32</v>
+        <v>6.17</v>
       </c>
       <c r="P22" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
         <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
         <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
         <v>1.73</v>
@@ -3090,22 +3090,22 @@
         <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.25</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3.26</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>4.52</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
-        <v>5.98</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="T24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.45</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="AC24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC25" t="n">
         <v>3.3</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>2.99</v>
       </c>
       <c r="P26" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.4</v>
+        <v>3.96</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.08</v>
+        <v>1.46</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="V28" t="n">
-        <v>4.7</v>
+        <v>3.94</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
         <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.42</v>
+        <v>3.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
-        <v>1.65</v>
+        <v>2.74</v>
       </c>
       <c r="P29" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="U29" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.56</v>
+        <v>1.55</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="R11" t="n">
         <v>1.22</v>
@@ -1766,19 +1766,19 @@
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
         <v>2.38</v>
@@ -1790,13 +1790,13 @@
         <v>1.46</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
         <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>6.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.22</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2099,7 +2099,7 @@
         <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
         <v>2.55</v>
@@ -2111,13 +2111,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="W14" t="n">
         <v>1.14</v>
@@ -2129,25 +2129,25 @@
         <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.48</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AG14" t="n">
         <v>1.24</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.33</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.11</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.06</v>
+        <v>5.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="T16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.78</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.62</v>
+        <v>3.66</v>
       </c>
       <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.34</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.07</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="O18" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.05</v>
+        <v>3.47</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,70 +2682,70 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.45</v>
+        <v>5.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T19" t="n">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
         <v>2.21</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.13</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.63</v>
+        <v>4.74</v>
       </c>
       <c r="AD20" t="n">
         <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,49 +3039,49 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>6.17</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
         <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="AA22" t="n">
         <v>1.73</v>
@@ -3090,22 +3090,22 @@
         <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="P24" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.78</v>
+        <v>3.76</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.44</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.4</v>
+        <v>3.26</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="P25" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
         <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
         <v>6.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
         <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>2.99</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.54</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>3.94</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.96</v>
+        <v>6.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>1.83</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.46</v>
+        <v>3.56</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
-        <v>2.74</v>
+        <v>6.17</v>
       </c>
       <c r="P27" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.66</v>
+        <v>3.18</v>
       </c>
       <c r="T27" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.69</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="M3" t="n">
         <v>3.03</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="M5" t="n">
         <v>3.08</v>
@@ -1376,7 +1376,7 @@
         <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
         <v>2.65</v>
@@ -1412,7 +1412,7 @@
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
         <v>1.95</v>
@@ -1436,7 +1436,7 @@
         <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
         <v>1.34</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.22</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>6.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.11</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.06</v>
+        <v>5.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="T15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.1</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,70 +2325,70 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.45</v>
+        <v>5.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
         <v>2.21</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="O17" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>3.47</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>2.41</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>3.06</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.62</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>3.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.54</v>
+        <v>2.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.07</v>
+        <v>4.74</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.21</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.06</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.65</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
         <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.74</v>
+        <v>3.82</v>
       </c>
       <c r="AD20" t="n">
         <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.66</v>
+        <v>2.81</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>4.7</v>
+        <v>6.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.95</v>
+        <v>3.26</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.66</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>3.66</v>
       </c>
       <c r="T22" t="n">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.96</v>
+        <v>4.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>2.69</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.16</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>6.7</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>27</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.59</v>
+        <v>2.99</v>
       </c>
       <c r="P23" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="U23" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>4.65</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.9</v>
+        <v>3.96</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.52</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>2.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.76</v>
+        <v>1.78</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>3.44</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.37</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.91</v>
+        <v>1.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>1.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>3.94</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.12</v>
+        <v>1.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>3.56</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.65</v>
+        <v>6.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>2.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>3.94</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.56</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="M12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.45</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O12" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
         <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.12</v>
@@ -1891,22 +1891,22 @@
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD12" t="n">
         <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
         <v>2.32</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
         <v>2.04</v>
@@ -1983,13 +1983,13 @@
         <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.22</v>
+        <v>5.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>2.39</v>
@@ -1998,10 +1998,10 @@
         <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
@@ -2013,25 +2013,25 @@
         <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AC13" t="n">
         <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
         <v>2.45</v>
@@ -2105,10 +2105,10 @@
         <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
         <v>2.17</v>
@@ -2123,7 +2123,7 @@
         <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.15</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.45</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
         <v>2.95</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>6.05</v>
+        <v>6.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.58</v>
+        <v>3.47</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.21</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2447,70 +2447,70 @@
         <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.36</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.11</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.06</v>
+        <v>5.35</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.5</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>6.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.82</v>
+        <v>2.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.42</v>
+        <v>2.01</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>8.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>5.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>1.26</v>
       </c>
       <c r="O22" t="n">
-        <v>2.74</v>
+        <v>7.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>1.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.66</v>
+        <v>3.44</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
         <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.69</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>13</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>1.59</v>
       </c>
       <c r="P24" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.78</v>
+        <v>9.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.08</v>
+        <v>4.08</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.73</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>3.77</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.99</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V25" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.56</v>
+        <v>1.58</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>1.85</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>6.17</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.12</v>
+        <v>7.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>3.94</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.98</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>3.17</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>2.34</v>
       </c>
       <c r="M28" t="n">
-        <v>6.7</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.59</v>
+        <v>2.56</v>
       </c>
       <c r="P28" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.5</v>
+        <v>2.99</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="T28" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="U28" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
         <v>1.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AB28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.52</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="O29" t="n">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.85</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AD29" t="n">
         <v>1.39</v>
       </c>
-      <c r="V29" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.62</v>
+        <v>5.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="T16" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
         <v>7.9</v>
@@ -2480,37 +2480,37 @@
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.38</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.41</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>3.06</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC19" t="n">
         <v>3.07</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.74</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>2.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>2.83</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.35</v>
+        <v>3.31</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>6.05</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.83</v>
+        <v>3.76</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.6</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="O22" t="n">
-        <v>7.4</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="N24" t="n">
-        <v>13</v>
+        <v>1.26</v>
       </c>
       <c r="O24" t="n">
-        <v>1.59</v>
+        <v>7.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.5</v>
+        <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="T24" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.08</v>
+        <v>1.08</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M26" t="n">
         <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>3.94</v>
+        <v>4.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
         <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.17</v>
+        <v>4.08</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>6.18</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.12</v>
+        <v>3.77</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="T27" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W27" t="n">
         <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.34</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.99</v>
+        <v>7.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="V28" t="n">
-        <v>4.7</v>
+        <v>3.94</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>3.17</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.48</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AC29" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="P11" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
         <v>2.22</v>
@@ -1763,40 +1763,40 @@
         <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
         <v>1.46</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
         <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.55</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.22</v>
-      </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>5.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z13" t="n">
         <v>4.2</v>
       </c>
-      <c r="N13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>5.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
         <v>2.95</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>6.6</v>
+        <v>6.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.33</v>
+        <v>2.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>2.01</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>3.11</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.35</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>6.05</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.83</v>
+        <v>3.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="O17" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.38</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.98</v>
+        <v>3.47</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="M24" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.26</v>
       </c>
-      <c r="O24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.08</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.59</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.5</v>
+        <v>3.77</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.58</v>
+        <v>2.81</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>4.65</v>
+        <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>3.26</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.08</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>1.59</v>
       </c>
       <c r="P27" t="n">
-        <v>2.22</v>
+        <v>2.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.77</v>
+        <v>9.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>3.58</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="V27" t="n">
-        <v>6.25</v>
+        <v>4.65</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.26</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.58</v>
+        <v>4.08</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="N28" t="n">
-        <v>9.300000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="O28" t="n">
-        <v>1.65</v>
+        <v>7.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.1</v>
+        <v>1.74</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="U28" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="V28" t="n">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.17</v>
+        <v>1.08</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.34</v>
+        <v>1.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.99</v>
+        <v>7.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="V29" t="n">
-        <v>4.7</v>
+        <v>3.94</v>
       </c>
       <c r="W29" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.56</v>
+        <v>3.17</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1739,10 +1739,10 @@
         <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
@@ -1751,19 +1751,19 @@
         <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
@@ -1772,7 +1772,7 @@
         <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.55</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="M12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
         <v>4.2</v>
       </c>
-      <c r="N12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5</v>
-      </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.55</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.22</v>
-      </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>5.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.35</v>
+        <v>5.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
         <v>3.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
         <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="O16" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>4.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.82</v>
+        <v>4.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.38</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z17" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
         <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>3.45</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>6.65</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.57</v>
+        <v>3.47</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.74</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.62</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AC19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.83</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.76</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.99</v>
+        <v>3.58</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.66</v>
+        <v>2.81</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>4.7</v>
+        <v>6.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.95</v>
+        <v>3.59</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>3.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="O24" t="n">
-        <v>6.18</v>
+        <v>7.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="T24" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.77</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="U26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.38</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.2</v>
+        <v>2.34</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.59</v>
+        <v>2.56</v>
       </c>
       <c r="P27" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.5</v>
+        <v>2.99</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="U27" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.08</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8.6</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>1.26</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>7.4</v>
+        <v>1.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.74</v>
+        <v>7.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>3.94</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.46</v>
+        <v>1.92</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.08</v>
+        <v>3.17</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M29" t="n">
         <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="P29" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="V29" t="n">
-        <v>3.94</v>
+        <v>4.65</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
         <v>1.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.17</v>
+        <v>4.08</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1849,28 +1849,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
         <v>2.42</v>
@@ -1879,7 +1879,7 @@
         <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.12</v>
@@ -1891,31 +1891,31 @@
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
         <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
         <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
         <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -2111,13 +2111,13 @@
         <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="W14" t="n">
         <v>1.14</v>
@@ -2132,28 +2132,28 @@
         <v>4.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
         <v>2.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
         <v>1.48</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46001.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>3.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.55</v>
+        <v>3.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.07</v>
+        <v>3.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2334,16 +2334,16 @@
         <v>3.13</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
         <v>2.45</v>
@@ -2352,10 +2352,10 @@
         <v>3.35</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V16" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
@@ -2367,7 +2367,7 @@
         <v>1.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AA16" t="n">
         <v>2.2</v>
@@ -2376,22 +2376,22 @@
         <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="AD16" t="n">
         <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.06</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.31</v>
+        <v>4.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>3.02</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.75</v>
+        <v>2.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>6.65</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>3.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.38</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>6.65</v>
       </c>
       <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.02</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>6.05</v>
+        <v>6.85</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>6.18</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>3.31</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.95</v>
+        <v>3.51</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.35</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3.31</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.06</v>
+        <v>2.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8.6</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>5.25</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.74</v>
+        <v>2.92</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.08</v>
+        <v>1.46</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.34</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.56</v>
+        <v>1.62</v>
       </c>
       <c r="P27" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.99</v>
+        <v>7.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>3.66</v>
+        <v>4.33</v>
       </c>
       <c r="T27" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="V27" t="n">
-        <v>4.7</v>
+        <v>3.94</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.95</v>
+        <v>6.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>3.72</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>9.300000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="O28" t="n">
-        <v>1.65</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>2.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.1</v>
+        <v>3.32</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>2.81</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>3.94</v>
+        <v>6.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.98</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.92</v>
+        <v>3.31</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.92</v>
+        <v>1.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.17</v>
+        <v>1.58</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.59</v>
+        <v>7.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.5</v>
+        <v>1.78</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
         <v>1.63</v>
       </c>
       <c r="V29" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.08</v>
+        <v>1.08</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>6.09</v>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.77</v>
+        <v>2.12</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="W30" t="n">
         <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="M5" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.2</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>9.800000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.57</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.44</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.21</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>6.65</v>
       </c>
       <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.02</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.4</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V19" t="n">
-        <v>6.65</v>
+        <v>6.85</v>
       </c>
       <c r="W19" t="n">
         <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="AA19" t="n">
         <v>1.83</v>
@@ -2733,22 +2733,22 @@
         <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>2.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.25</v>
+        <v>4.35</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>6.85</v>
+        <v>6.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>3.24</v>
       </c>
       <c r="T21" t="n">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.16</v>
       </c>
-      <c r="M25" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="N25" t="n">
-        <v>27</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH25" t="n">
-        <v>4.7</v>
+        <v>3.72</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="N27" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="O27" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="P27" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="U27" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.35</v>
+        <v>5.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>6.09</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.32</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>6.75</v>
+        <v>6.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.31</v>
+        <v>2.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>7.5</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="U29" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>3.51</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.08</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.85</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
-        <v>6.09</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2.49</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V30" t="n">
-        <v>6.45</v>
+        <v>6.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.84</v>
+        <v>3.31</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="M6" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N15" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="R15" t="n">
         <v>1.52</v>
@@ -2233,10 +2233,10 @@
         <v>3.35</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
@@ -2248,28 +2248,28 @@
         <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
         <v>1.53</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.06</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.76</v>
+        <v>4.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.56</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.75</v>
+        <v>2.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>6.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.4</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V18" t="n">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
         <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.2</v>
+        <v>3.06</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.25</v>
+        <v>3.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>6.85</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.07</v>
+        <v>3.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.44</v>
       </c>
-      <c r="V20" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.21</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7.5</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.45</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.08</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="M25" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.5</v>
+        <v>3.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>4.33</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>3.94</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.97</v>
+        <v>3.31</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.72</v>
+        <v>1.52</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>7.5</v>
       </c>
       <c r="P26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.18</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
         <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.61</v>
+        <v>1.08</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.16</v>
+        <v>1.88</v>
       </c>
       <c r="M27" t="n">
-        <v>6.7</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>27</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>1.54</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
         <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE27" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.71</v>
+        <v>2.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.7</v>
+        <v>1.61</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>6.7</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
-        <v>6.09</v>
+        <v>1.54</v>
       </c>
       <c r="P28" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>7.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>6.45</v>
+        <v>4.4</v>
       </c>
       <c r="W28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.08</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>6.09</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="T29" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>7.1</v>
+        <v>6.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.51</v>
+        <v>2.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.64</v>
+        <v>1.14</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1730,19 +1730,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="P11" t="n">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
@@ -1760,7 +1760,7 @@
         <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>3.23</v>
       </c>
       <c r="O13" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
         <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
         <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.39</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.02</v>
+        <v>3.64</v>
       </c>
       <c r="N15" t="n">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="P15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.95</v>
       </c>
       <c r="T16" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>6.05</v>
+        <v>6.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.75</v>
+        <v>3.47</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.21</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>3.35</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>6.65</v>
+        <v>9.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.47</v>
+        <v>2.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>4.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>2.2</v>
@@ -2608,7 +2608,7 @@
         <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
         <v>1.91</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
         <v>3.06</v>
@@ -2700,31 +2700,31 @@
         <v>3.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
         <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
         <v>2.05</v>
@@ -2733,7 +2733,7 @@
         <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
         <v>1.25</v>
@@ -2804,13 +2804,13 @@
         <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
         <v>1.93</v>
@@ -2819,10 +2819,10 @@
         <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="T20" t="n">
         <v>3</v>
@@ -2831,13 +2831,13 @@
         <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
         <v>1.34</v>
@@ -2855,13 +2855,13 @@
         <v>3.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
         <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
         <v>1.44</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>6.09</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>6.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.51</v>
+        <v>2.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.37</v>
+        <v>2.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3277,40 +3277,40 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="P24" t="n">
         <v>2.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3319,7 +3319,7 @@
         <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.35</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
         <v>1.4</v>
@@ -3328,22 +3328,22 @@
         <v>2.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.37</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>17</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="P25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.31</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.52</v>
+        <v>4.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>2.22</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
-        <v>7.5</v>
+        <v>2.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="U26" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="R27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.25</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z27" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>3.31</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="T14" t="n">
         <v>2.3</v>
@@ -2117,25 +2117,25 @@
         <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC14" t="n">
         <v>2.4</v>
@@ -2144,16 +2144,16 @@
         <v>1.55</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46001.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.35</v>
+        <v>5.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.38</v>
       </c>
-      <c r="V16" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z16" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="N17" t="n">
-        <v>3.13</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="P17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,49 +2563,49 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>6.9</v>
+        <v>6.65</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="AA18" t="n">
         <v>1.83</v>
@@ -2614,22 +2614,22 @@
         <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="O19" t="n">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.76</v>
+        <v>4.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>3.35</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>9.9</v>
       </c>
       <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.08</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>4.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.69</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>3.47</v>
+        <v>5.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.44</v>
+        <v>8.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.93</v>
+        <v>7.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.24</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>1.99</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.1</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>3.84</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.4</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
-        <v>6.09</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.3</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.84</v>
-      </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.84</v>
+        <v>3.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.32</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>8.1</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>1.6</v>
+        <v>6.09</v>
       </c>
       <c r="P24" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.6</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>4</v>
+        <v>6.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>3.84</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>2.44</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.84</v>
+        <v>1.13</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.35</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q27" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="V27" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.31</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.31</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V30" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.14</v>
+        <v>5.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.63</v>
+        <v>1.08</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.85</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>5.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1730,31 +1730,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.66</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
@@ -1778,25 +1778,25 @@
         <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>5.03</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.14</v>
@@ -1888,34 +1888,34 @@
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
         <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
-        <v>3.77</v>
+        <v>4.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
         <v>3.42</v>
@@ -1998,7 +1998,7 @@
         <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.12</v>
@@ -2013,19 +2013,19 @@
         <v>4.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AF13" t="n">
         <v>2.44</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>4.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.04</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.44</v>
+        <v>4.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
         <v>2.94</v>
@@ -2343,43 +2343,43 @@
         <v>3.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>6.1</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
         <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
         <v>1.78</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="M17" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="O17" t="n">
-        <v>2.13</v>
+        <v>2.92</v>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.35</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>5.9</v>
+        <v>6.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>3.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
         <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2682,28 +2682,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="T19" t="n">
         <v>3.35</v>
@@ -2715,34 +2715,34 @@
         <v>9.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
         <v>4.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
         <v>1.36</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>5.06</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>2.18</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>4.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>6.85</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.78</v>
+        <v>3.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>8.4</v>
       </c>
       <c r="M21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1</v>
+        <v>1.34</v>
       </c>
       <c r="O21" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.6</v>
+        <v>1.78</v>
       </c>
       <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.15</v>
       </c>
-      <c r="S21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.87</v>
       </c>
-      <c r="V21" t="n">
-        <v>4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.84</v>
+        <v>1.08</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>2.81</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>4.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.31</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="N25" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T25" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="V25" t="n">
-        <v>4.6</v>
+        <v>3.94</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.05</v>
+        <v>6.4</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.7</v>
+        <v>3.72</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.81</v>
+        <v>1.56</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>4.77</v>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="T27" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="V27" t="n">
-        <v>4.5</v>
+        <v>6.45</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.73</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="M28" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.64</v>
+        <v>3.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V29" t="n">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.199999999999999</v>
+        <v>2.89</v>
       </c>
       <c r="M30" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>1.33</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
-        <v>7.5</v>
+        <v>3.44</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.78</v>
+        <v>2.89</v>
       </c>
       <c r="R30" t="n">
         <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="U30" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>5.93</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="N8" t="n">
-        <v>5.93</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>4.08</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="P12" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.03</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>5.03</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.56</v>
       </c>
-      <c r="V13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>2.1</v>
+        <v>2.92</v>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.35</v>
+        <v>3.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>5.9</v>
+        <v>6.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.04</v>
+        <v>3.54</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.76</v>
+        <v>4.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>4.71</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.4</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>5.06</v>
       </c>
       <c r="O18" t="n">
-        <v>3.42</v>
+        <v>2.18</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.06</v>
+        <v>4.83</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>6.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.78</v>
+        <v>3.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.43</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="Q19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
         <v>4.04</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.46</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>2.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.71</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.64</v>
+        <v>2.38</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.06</v>
+        <v>2.94</v>
       </c>
       <c r="O20" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.83</v>
+        <v>3.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>6.85</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.99</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.4</v>
+        <v>2.36</v>
       </c>
       <c r="M21" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
         <v>7.2</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.08</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="M22" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="O22" t="n">
-        <v>1.55</v>
+        <v>4.77</v>
       </c>
       <c r="P22" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.5</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>4.6</v>
+        <v>6.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.21</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="O27" t="n">
-        <v>4.77</v>
+        <v>7.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="V27" t="n">
-        <v>6.45</v>
+        <v>5.1</v>
       </c>
       <c r="W27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N28" t="n">
         <v>2.36</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.7</v>
       </c>
-      <c r="O28" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>7.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.64</v>
+        <v>10.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="U29" t="n">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="V29" t="n">
-        <v>6.75</v>
+        <v>4.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.56</v>
+        <v>5.21</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>3.44</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.89</v>
+        <v>3.64</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="T30" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="V30" t="n">
-        <v>5.9</v>
+        <v>6.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
         <v>3.08</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>5.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.4</v>
       </c>
-      <c r="V15" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.71</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>5.06</v>
       </c>
       <c r="O17" t="n">
-        <v>3.42</v>
+        <v>2.18</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.06</v>
+        <v>4.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>6.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.78</v>
+        <v>3.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>2.43</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>5.06</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.83</v>
+        <v>4.04</v>
       </c>
       <c r="R18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.36</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2804,70 +2804,70 @@
         <v>2.38</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.76</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T20" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>6.65</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="O22" t="n">
-        <v>4.77</v>
+        <v>7.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>6.45</v>
+        <v>5.1</v>
       </c>
       <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.89</v>
+        <v>5.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.36</v>
+        <v>1.56</v>
       </c>
       <c r="O28" t="n">
-        <v>3.44</v>
+        <v>4.77</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.89</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="T28" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>5.9</v>
+        <v>6.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -1730,31 +1730,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>3.66</v>
       </c>
       <c r="O11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
         <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
@@ -1766,7 +1766,7 @@
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.18</v>
@@ -1778,25 +1778,25 @@
         <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
         <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>4.08</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="P12" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>5.03</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.56</v>
       </c>
-      <c r="V12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>4.08</v>
       </c>
       <c r="N13" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="P13" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.03</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.06</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.46</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>4.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,34 +2325,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
         <v>7.9</v>
@@ -2361,37 +2361,37 @@
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>5.06</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.83</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>6.85</v>
+        <v>6.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
         <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.21</v>
+        <v>1.56</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.43</v>
+        <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>3.64</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.15</v>
+        <v>2.11</v>
       </c>
       <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V18" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="O20" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.49</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>2.67</v>
+        <v>1.68</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>4.65</v>
+        <v>3.94</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.52</v>
+        <v>3.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.48</v>
+        <v>3.72</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.89</v>
+        <v>5.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.36</v>
+        <v>1.56</v>
       </c>
       <c r="O25" t="n">
-        <v>3.44</v>
+        <v>4.77</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.89</v>
+        <v>2.08</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="T25" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
-        <v>5.9</v>
+        <v>6.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.5</v>
+        <v>2.49</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
-        <v>4.77</v>
+        <v>2.67</v>
       </c>
       <c r="P28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.84</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3991,16 +3991,16 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
         <v>2.05</v>
@@ -4009,37 +4009,37 @@
         <v>3.64</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
         <v>1.39</v>
       </c>
       <c r="V30" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="W30" t="n">
         <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
         <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
         <v>3.3</v>
@@ -4051,13 +4051,13 @@
         <v>1.69</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1314,7 +1314,7 @@
         <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
         <v>1.35</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>5.93</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1748,13 +1748,13 @@
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
         <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
@@ -1787,7 +1787,7 @@
         <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
         <v>2.4</v>
@@ -1796,7 +1796,7 @@
         <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.77</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>3.23</v>
       </c>
       <c r="O12" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="P12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.49</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.66</v>
+        <v>1.87</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T15" t="n">
         <v>3.1</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="AA15" t="n">
         <v>2.2</v>
@@ -2257,22 +2257,22 @@
         <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.73</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,49 +2325,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>3.13</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="AA16" t="n">
         <v>2.2</v>
@@ -2376,22 +2376,22 @@
         <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2456,25 +2456,25 @@
         <v>2.63</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.65</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V17" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="W17" t="n">
         <v>1.05</v>
@@ -2501,13 +2501,13 @@
         <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
         <v>1.99</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
         <v>1.56</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.41</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>2.99</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>2.28</v>
+        <v>2.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.67</v>
+        <v>3.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.22</v>
+        <v>1.48</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
-        <v>2.99</v>
+        <v>3.64</v>
       </c>
       <c r="N20" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.66</v>
+        <v>5.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.48</v>
+        <v>2.23</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.4</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>5.4</v>
+        <v>3.78</v>
       </c>
       <c r="N22" t="n">
-        <v>1.34</v>
+        <v>2.81</v>
       </c>
       <c r="O22" t="n">
-        <v>7.2</v>
+        <v>2.67</v>
       </c>
       <c r="P22" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>3.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>5.1</v>
+        <v>4.65</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>1.33</v>
       </c>
       <c r="O23" t="n">
-        <v>1.68</v>
+        <v>8.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>1.77</v>
       </c>
       <c r="R23" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="V23" t="n">
-        <v>3.94</v>
+        <v>5.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.72</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="O25" t="n">
-        <v>4.77</v>
+        <v>5.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.89</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>3.44</v>
+        <v>2.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.89</v>
+        <v>3.64</v>
       </c>
       <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="O27" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="V27" t="n">
-        <v>7.2</v>
+        <v>5.75</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.2</v>
+        <v>2.31</v>
       </c>
       <c r="M29" t="n">
-        <v>7.5</v>
+        <v>3.31</v>
       </c>
       <c r="N29" t="n">
-        <v>15</v>
+        <v>2.98</v>
       </c>
       <c r="O29" t="n">
-        <v>1.55</v>
+        <v>2.99</v>
       </c>
       <c r="P29" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>10.5</v>
+        <v>3.46</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.21</v>
+        <v>1.62</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>1.32</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>8.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.95</v>
+        <v>1.65</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.64</v>
+        <v>7.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="U30" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="V30" t="n">
-        <v>6.8</v>
+        <v>3.94</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.92</v>
+        <v>3.09</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.55</v>
+        <v>3.92</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -677,31 +677,31 @@
         <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA2" t="n">
         <v>2.05</v>
@@ -710,22 +710,22 @@
         <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46001.375</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>4.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -906,40 +906,40 @@
         <v>3.68</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA4" t="n">
         <v>2.35</v>
@@ -948,22 +948,22 @@
         <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46001.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="M5" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.4</v>
+        <v>2.99</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1510,31 +1510,31 @@
         <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
         <v>2.19</v>
@@ -1543,22 +1543,22 @@
         <v>1.59</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46001.45833333334</v>
@@ -1629,31 +1629,31 @@
         <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA10" t="n">
         <v>2</v>
@@ -1662,22 +1662,22 @@
         <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46001.5</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
         <v>3.12</v>
@@ -2105,22 +2105,22 @@
         <v>2.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
         <v>3.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="U14" t="n">
         <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>5.15</v>
+        <v>4.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
@@ -2129,25 +2129,25 @@
         <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.55</v>
+        <v>4.87</v>
       </c>
       <c r="AA14" t="n">
         <v>1.57</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.33</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
         <v>1.53</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,49 +2444,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.43</v>
-      </c>
       <c r="V17" t="n">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="AA17" t="n">
         <v>1.83</v>
@@ -2495,22 +2495,22 @@
         <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.56</v>
+        <v>2.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,49 +2563,49 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>6.9</v>
+        <v>6.65</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AA18" t="n">
         <v>1.83</v>
@@ -2614,22 +2614,22 @@
         <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.22</v>
+        <v>1.56</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.19</v>
+        <v>2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>5.9</v>
+        <v>3.78</v>
       </c>
       <c r="N21" t="n">
-        <v>17</v>
+        <v>2.81</v>
       </c>
       <c r="O21" t="n">
-        <v>1.54</v>
+        <v>2.67</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>3.04</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -2944,49 +2944,49 @@
         <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
         <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE21" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.64</v>
+        <v>2.73</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.2</v>
+        <v>1.47</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>2.69</v>
       </c>
       <c r="M22" t="n">
-        <v>3.78</v>
+        <v>3.47</v>
       </c>
       <c r="N22" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="O22" t="n">
-        <v>2.67</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
-        <v>4.65</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8.199999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="M23" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.33</v>
+        <v>8.1</v>
       </c>
       <c r="O23" t="n">
-        <v>8.1</v>
+        <v>1.65</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.77</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="V23" t="n">
-        <v>5.1</v>
+        <v>3.94</v>
       </c>
       <c r="W23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.15</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.05</v>
+        <v>3.92</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O24" t="n">
-        <v>5.5</v>
+        <v>1.54</v>
       </c>
       <c r="P24" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="W24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.12</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>5.2</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.27</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>1.51</v>
+        <v>2.92</v>
       </c>
       <c r="O25" t="n">
-        <v>5.15</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.07</v>
+        <v>3.64</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,49 +3634,49 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.69</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.47</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.44</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="V27" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA27" t="n">
         <v>1.73</v>
@@ -3685,22 +3685,22 @@
         <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
         <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.31</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="AC29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.32</v>
+        <v>5.27</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>8.1</v>
+        <v>1.51</v>
       </c>
       <c r="O30" t="n">
-        <v>1.65</v>
+        <v>5.15</v>
       </c>
       <c r="P30" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.5</v>
+        <v>2.07</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>3.94</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.92</v>
+        <v>1.12</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.2</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AB3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.18</v>
       </c>
-      <c r="V3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE3" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.93</v>
+        <v>2.99</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="N4" t="n">
-        <v>3.68</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46001.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.17</v>
+        <v>1.93</v>
       </c>
       <c r="M5" t="n">
         <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.12</v>
+        <v>3.68</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75</v>
+        <v>2.73</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>4.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>4.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>2.98</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.42</v>
+        <v>2.28</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.78</v>
+        <v>3.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="N16" t="n">
-        <v>3.13</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.98</v>
+        <v>5.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
         <v>1</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.54</v>
+        <v>3.72</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.51</v>
+        <v>2.23</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="M17" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="O17" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>3.98</v>
       </c>
       <c r="R17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.36</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>6.65</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.64</v>
+        <v>2.99</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.41</v>
+        <v>3.66</v>
       </c>
       <c r="R20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.33</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.47</v>
-      </c>
       <c r="V20" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF20" t="n">
         <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.23</v>
+        <v>1.48</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.22</v>
+        <v>1.19</v>
       </c>
       <c r="M21" t="n">
-        <v>3.78</v>
+        <v>5.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.81</v>
+        <v>17</v>
       </c>
       <c r="O21" t="n">
-        <v>2.67</v>
+        <v>1.54</v>
       </c>
       <c r="P21" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.04</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -2944,49 +2944,49 @@
         <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
         <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.12</v>
       </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.47</v>
+        <v>5.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.69</v>
+        <v>1.32</v>
       </c>
       <c r="M22" t="n">
-        <v>3.47</v>
+        <v>5.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>8.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>1.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>5.75</v>
+        <v>3.94</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>3.09</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.69</v>
+        <v>1.87</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>3.92</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.19</v>
       </c>
-      <c r="M24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>17</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>11</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH24" t="n">
-        <v>5.2</v>
+        <v>1.05</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N25" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.64</v>
+        <v>3.46</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.05</v>
       </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>2.35</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
-        <v>5.5</v>
+        <v>2.95</v>
       </c>
       <c r="P27" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>3.64</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="T27" t="n">
-        <v>2.35</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
         <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="M28" t="n">
-        <v>3.31</v>
+        <v>3.78</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>2.67</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.46</v>
+        <v>3.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.93</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>4.65</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="M29" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
-        <v>8.1</v>
+        <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
         <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="T29" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="U29" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.45</v>
+        <v>3.84</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.27</v>
+        <v>2.69</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N30" t="n">
-        <v>1.51</v>
+        <v>2.44</v>
       </c>
       <c r="O30" t="n">
-        <v>5.15</v>
+        <v>3.35</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T30" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
         <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>4.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.85</v>
+        <v>5.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.4</v>
+        <v>3.17</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2.2</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="AB6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.18</v>
       </c>
-      <c r="V6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE6" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>2.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>6.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>4.6</v>
+        <v>3.54</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.7</v>
+        <v>4.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>2.31</v>
+        <v>3.84</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.05</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>3.54</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.52</v>
+        <v>3.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.95</v>
+        <v>7.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="O15" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>6.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AA15" t="n">
         <v>1.83</v>
@@ -2257,22 +2257,22 @@
         <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.22</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.64</v>
+        <v>2.99</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>2.11</v>
+        <v>2.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.41</v>
+        <v>3.66</v>
       </c>
       <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.47</v>
-      </c>
       <c r="V16" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.23</v>
+        <v>1.48</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>2.98</v>
+        <v>3.64</v>
       </c>
       <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.5</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.78</v>
+        <v>3.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.82</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.42</v>
+        <v>2.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="N19" t="n">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>2.99</v>
+        <v>3.78</v>
       </c>
       <c r="N20" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>2.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.66</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.48</v>
+        <v>2.22</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.19</v>
       </c>
-      <c r="M21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N21" t="n">
-        <v>17</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>11</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH21" t="n">
-        <v>5.2</v>
+        <v>1.05</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8.199999999999999</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>5.1</v>
+        <v>3.31</v>
       </c>
       <c r="N24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.33</v>
       </c>
-      <c r="O24" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z24" t="n">
-        <v>4.45</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.27</v>
+        <v>1.19</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="N26" t="n">
-        <v>1.51</v>
+        <v>17</v>
       </c>
       <c r="O26" t="n">
-        <v>5.15</v>
+        <v>1.54</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.07</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.11</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.12</v>
+        <v>5.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.28</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
         <v>2.88</v>
@@ -704,10 +704,10 @@
         <v>3.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
         <v>3.28</v>
@@ -716,16 +716,16 @@
         <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
         <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46001.375</v>
@@ -787,7 +787,7 @@
         <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>5.2</v>
+        <v>5.52</v>
       </c>
       <c r="P3" t="n">
         <v>1.81</v>
@@ -796,10 +796,10 @@
         <v>2.69</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
         <v>3.84</v>
@@ -808,7 +808,7 @@
         <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
@@ -823,10 +823,10 @@
         <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC3" t="n">
         <v>5.65</v>
@@ -838,7 +838,7 @@
         <v>2.32</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
         <v>1.31</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.99</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46001.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.93</v>
+        <v>2.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.68</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.73</v>
+        <v>3.88</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.62</v>
+        <v>2.85</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="U5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.26</v>
       </c>
-      <c r="V5" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.17</v>
+        <v>2.99</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.65</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>5.7</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>2.31</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.05</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.54</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.52</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.95</v>
+        <v>7.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.85</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84</v>
+        <v>2.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>5.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>3.46</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>2.47</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.24</v>
       </c>
-      <c r="AC8" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1492,28 +1492,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>4.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
         <v>3.2</v>
@@ -1528,7 +1528,7 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.39</v>
@@ -1537,25 +1537,25 @@
         <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD9" t="n">
         <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
         <v>1.54</v>
@@ -1611,34 +1611,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
         <v>7.3</v>
@@ -1650,16 +1650,16 @@
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
         <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
         <v>3.42</v>
@@ -1668,16 +1668,16 @@
         <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46001.5</v>
@@ -1754,7 +1754,7 @@
         <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
@@ -1796,7 +1796,7 @@
         <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>3.77</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.23</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="P12" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.87</v>
+        <v>3.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="M13" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z13" t="n">
         <v>4.3</v>
       </c>
-      <c r="N13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.9</v>
+        <v>1.87</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="N15" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="O15" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
         <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>2.99</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.91</v>
+        <v>2.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.66</v>
+        <v>4.83</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="N17" t="n">
-        <v>3.13</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.98</v>
+        <v>5.41</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.54</v>
+        <v>3.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.61</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>2.11</v>
+        <v>2.63</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.41</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2715,7 +2715,7 @@
         <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
@@ -2736,7 +2736,7 @@
         <v>3.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
         <v>1.85</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="O20" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.36</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.199999999999999</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
-        <v>5.1</v>
+        <v>3.31</v>
       </c>
       <c r="N21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.33</v>
       </c>
-      <c r="O21" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="Z21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.28</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.32</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>8.1</v>
+        <v>1.57</v>
       </c>
       <c r="O22" t="n">
-        <v>1.65</v>
+        <v>5.7</v>
       </c>
       <c r="P22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.87</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>2.46</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.92</v>
+        <v>1.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.27</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="N23" t="n">
-        <v>1.51</v>
+        <v>17</v>
       </c>
       <c r="O23" t="n">
-        <v>5.15</v>
+        <v>1.53</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.07</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.12</v>
+        <v>5.05</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.19</v>
+        <v>5.27</v>
       </c>
       <c r="M26" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>17</v>
+        <v>1.51</v>
       </c>
       <c r="O26" t="n">
-        <v>1.54</v>
+        <v>5.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.67</v>
       </c>
-      <c r="V26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.92</v>
+        <v>1.33</v>
       </c>
       <c r="O27" t="n">
-        <v>2.95</v>
+        <v>5.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.64</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="V27" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>3.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3762,37 +3762,37 @@
         <v>2.81</v>
       </c>
       <c r="O28" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
         <v>3.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
         <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V28" t="n">
         <v>4.65</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
         <v>5</v>
@@ -3816,10 +3816,10 @@
         <v>2.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,49 +3872,49 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>2.69</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>2.44</v>
       </c>
       <c r="O29" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="T29" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
         <v>5.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
         <v>1.73</v>
@@ -3923,22 +3923,22 @@
         <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AD29" t="n">
         <v>1.42</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>3.62</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U30" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="V30" t="n">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
-        <v>5.52</v>
+        <v>3.76</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.84</v>
+        <v>3.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.65</v>
+        <v>4.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>2.73</v>
+        <v>3.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.67</v>
+        <v>2.85</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="U4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.26</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46001.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M5" t="n">
         <v>2.95</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>3.88</v>
+        <v>2.73</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.85</v>
+        <v>4.67</v>
       </c>
       <c r="R5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.42</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="Z5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.29</v>
       </c>
-      <c r="V5" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>4.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>6.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>4.6</v>
+        <v>3.54</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>2.49</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.24</v>
       </c>
-      <c r="AC7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.31</v>
+        <v>3.88</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.95</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="T8" t="n">
-        <v>3.46</v>
+        <v>4.65</v>
       </c>
       <c r="U8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.24</v>
       </c>
-      <c r="V8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AC8" t="n">
-        <v>4.8</v>
+        <v>7.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.28</v>
+        <v>2.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z12" t="n">
         <v>4.3</v>
       </c>
-      <c r="N12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AA12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.36</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.11</v>
+        <v>1.74</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.77</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.23</v>
+        <v>7.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="R13" t="n">
         <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V13" t="n">
-        <v>5.35</v>
+        <v>5.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.87</v>
+        <v>2.92</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>2.99</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.91</v>
+        <v>2.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.66</v>
+        <v>4.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
         <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.54</v>
+        <v>2.14</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.83</v>
+        <v>5.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.64</v>
+        <v>2.98</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.11</v>
+        <v>3.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.41</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.63</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.72</v>
       </c>
-      <c r="AF18" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>3.42</v>
+        <v>2.91</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.53</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.31</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>2.37</v>
       </c>
       <c r="O21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.73</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH22" t="n">
         <v>5.4</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>17</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.1</v>
+        <v>3.39</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.05</v>
+        <v>3.44</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.05</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.32</v>
+        <v>5.35</v>
       </c>
       <c r="M25" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>8.1</v>
+        <v>1.54</v>
       </c>
       <c r="O25" t="n">
-        <v>1.66</v>
+        <v>5.45</v>
       </c>
       <c r="P25" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.6</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.21</v>
       </c>
-      <c r="S25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V25" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Z25" t="n">
-        <v>6.3</v>
+        <v>3.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.09</v>
+        <v>2.12</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.33</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3524,64 +3524,64 @@
         <v>1.51</v>
       </c>
       <c r="O26" t="n">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.62</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8.199999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.33</v>
+        <v>2.32</v>
       </c>
       <c r="O27" t="n">
-        <v>5.9</v>
+        <v>3.46</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="V27" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.78</v>
+        <v>5.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.81</v>
+        <v>1.35</v>
       </c>
       <c r="O28" t="n">
-        <v>2.93</v>
+        <v>5.9</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.04</v>
+        <v>1.79</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="V28" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.73</v>
+        <v>1.88</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.54</v>
+        <v>3.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>9</v>
       </c>
       <c r="O30" t="n">
-        <v>2.96</v>
+        <v>1.66</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.62</v>
+        <v>7.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="V30" t="n">
-        <v>6.7</v>
+        <v>3.94</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.3</v>
+        <v>6.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.92</v>
+        <v>3.04</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.3</v>
+        <v>1.88</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.55</v>
+        <v>3.65</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="P2" t="n">
         <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.45</v>
+        <v>6.62</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,34 +698,34 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
         <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46001.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.98</v>
+        <v>4.33</v>
       </c>
       <c r="M3" t="n">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.76</v>
+        <v>5.57</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>3.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.51</v>
       </c>
-      <c r="AC3" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.88</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.42</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46001.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,61 +1016,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>2.73</v>
+        <v>3.76</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.67</v>
+        <v>3.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="U5" t="n">
         <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
         <v>2.01</v>
@@ -1079,10 +1079,10 @@
         <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>5.57</v>
+        <v>3.92</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.21</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.9</v>
+        <v>3.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>2.3</v>
+        <v>3.88</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.32</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="S7" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="T7" t="n">
-        <v>3.54</v>
+        <v>4.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="V7" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.88</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>6.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>4.65</v>
+        <v>3.54</v>
       </c>
       <c r="U8" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>2.49</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.24</v>
       </c>
-      <c r="AC8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
         <v>8.699999999999999</v>
@@ -1531,34 +1531,34 @@
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
         <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46001.45833333334</v>
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>4.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
         <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
         <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC10" t="n">
         <v>3.42</v>
@@ -1668,16 +1668,16 @@
         <v>1.23</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.81</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46001.5</v>
@@ -1733,10 +1733,10 @@
         <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
         <v>2.25</v>
@@ -1745,7 +1745,7 @@
         <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -1769,34 +1769,34 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
         <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
         <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>3.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="U14" t="n">
         <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
@@ -2129,13 +2129,13 @@
         <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.87</v>
+        <v>4.55</v>
       </c>
       <c r="AA14" t="n">
         <v>1.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC14" t="n">
         <v>2.33</v>
@@ -2144,10 +2144,10 @@
         <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AG14" t="n">
         <v>1.53</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>5.19</v>
       </c>
       <c r="O15" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="P15" t="n">
         <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.83</v>
+        <v>5.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.44</v>
+        <v>3.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.11</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.41</v>
+        <v>3.06</v>
       </c>
       <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.42</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
         <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.13</v>
+        <v>5.22</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.96</v>
+        <v>5.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.63</v>
+        <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.5</v>
+        <v>2.99</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.05</v>
+        <v>2.51</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
@@ -2831,31 +2831,31 @@
         <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="W20" t="n">
         <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
         <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AA20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
         <v>1.72</v>
@@ -2864,10 +2864,10 @@
         <v>2.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.65</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.93</v>
+        <v>7.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="U21" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
-        <v>4.45</v>
+        <v>3.94</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.05</v>
+        <v>6.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.51</v>
+        <v>3.65</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.08</v>
+        <v>2.65</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>16.5</v>
+        <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.93</v>
       </c>
-      <c r="Q22" t="n">
-        <v>11.2</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V22" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.27</v>
+        <v>1.41</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.66</v>
+        <v>2.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.4</v>
+        <v>1.51</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>5.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>5.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.64</v>
+        <v>3.12</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
         <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.35</v>
+        <v>1.08</v>
       </c>
       <c r="M25" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V25" t="n">
         <v>4</v>
       </c>
-      <c r="N25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O25" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.25</v>
-      </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.12</v>
+        <v>2.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.27</v>
+        <v>8.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="O26" t="n">
-        <v>5.45</v>
+        <v>5.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.17</v>
+        <v>3.24</v>
       </c>
       <c r="AH26" t="n">
         <v>1.09</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.75</v>
+        <v>5.27</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="O27" t="n">
-        <v>3.46</v>
+        <v>5.45</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.86</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
         <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>5.9</v>
+        <v>2.97</v>
       </c>
       <c r="P28" t="n">
-        <v>2.58</v>
+        <v>2.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.79</v>
+        <v>3.64</v>
       </c>
       <c r="R28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.28</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.24</v>
+        <v>1.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.33</v>
+        <v>2.98</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
-        <v>5.57</v>
+        <v>3.76</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="R3" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.9</v>
+        <v>4.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>4.33</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>5.57</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>2.73</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="S4" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46001.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.76</v>
+        <v>2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T5" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="O12" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
         <v>5.3</v>
@@ -1888,34 +1888,34 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
         <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AC12" t="n">
         <v>2.46</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="AG12" t="n">
         <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N13" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="P13" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
         <v>3.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.42</v>
       </c>
-      <c r="AC13" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2206,19 +2206,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
         <v>5.19</v>
       </c>
       <c r="O15" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
         <v>5.49</v>
@@ -2227,13 +2227,13 @@
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
         <v>5.9</v>
@@ -2245,19 +2245,19 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
         <v>1.35</v>
@@ -2266,13 +2266,13 @@
         <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.16</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.02</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>5.22</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.68</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>6.85</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.44</v>
+        <v>2.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.99</v>
+        <v>3.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AB19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.24</v>
       </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.49</v>
+        <v>2.24</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2920,52 +2920,52 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>5.75</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="V21" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.35</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AB21" t="n">
         <v>3.04</v>
@@ -2974,19 +2974,19 @@
         <v>1.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.65</v>
+        <v>3.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="P22" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.93</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.62</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="U22" t="n">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
-        <v>4.45</v>
+        <v>6.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.73</v>
+        <v>2.02</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.35</v>
+        <v>1.17</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>17.56</v>
       </c>
       <c r="O23" t="n">
-        <v>5.45</v>
+        <v>1.52</v>
       </c>
       <c r="P23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.29</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>1.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.64</v>
+        <v>3.12</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.39</v>
+        <v>3.86</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.08</v>
+        <v>7.6</v>
       </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>4.85</v>
       </c>
       <c r="N25" t="n">
-        <v>16.5</v>
+        <v>1.34</v>
       </c>
       <c r="O25" t="n">
-        <v>1.52</v>
+        <v>7.6</v>
       </c>
       <c r="P25" t="n">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.2</v>
+        <v>1.74</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>5.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8.4</v>
+        <v>2.26</v>
       </c>
       <c r="M26" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.35</v>
       </c>
-      <c r="O26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.63</v>
-      </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.45</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.35</v>
+        <v>3.44</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.24</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.27</v>
+        <v>2.82</v>
       </c>
       <c r="M27" t="n">
         <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>1.51</v>
+        <v>2.23</v>
       </c>
       <c r="O27" t="n">
-        <v>5.45</v>
+        <v>3.15</v>
       </c>
       <c r="P27" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="V27" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.33</v>
+        <v>5.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="O28" t="n">
-        <v>2.97</v>
+        <v>5.45</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.64</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="V28" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3872,37 +3872,37 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O29" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
         <v>1.51</v>
       </c>
       <c r="V29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="W29" t="n">
         <v>1.09</v>
@@ -3911,34 +3911,34 @@
         <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="AA29" t="n">
         <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>2.69</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.76</v>
+        <v>5.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.02</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.45</v>
+        <v>5.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>5.57</v>
+        <v>3.76</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.9</v>
+        <v>4.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
         <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
         <v>3.88</v>
@@ -1293,10 +1293,10 @@
         <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
         <v>3.34</v>
@@ -1376,19 +1376,19 @@
         <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="P8" t="n">
         <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.32</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
@@ -1397,31 +1397,31 @@
         <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
         <v>1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC8" t="n">
         <v>4.9</v>
@@ -1433,7 +1433,7 @@
         <v>2.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
         <v>1.24</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>5.19</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.49</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>3.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
         <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>5.19</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>5.49</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.18</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
         <v>1.76</v>
@@ -2388,10 +2388,10 @@
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="M17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.51</v>
-      </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.51</v>
+        <v>3.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="P20" t="n">
         <v>1.95</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.5</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.44</v>
+        <v>4.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>2.86</v>
       </c>
       <c r="M21" t="n">
-        <v>5.75</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>9.699999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.65</v>
+        <v>3.54</v>
       </c>
       <c r="P21" t="n">
-        <v>2.86</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.3</v>
+        <v>2.85</v>
       </c>
       <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.2</v>
       </c>
-      <c r="S21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.88</v>
+        <v>2.69</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.49</v>
+        <v>1.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.17</v>
       </c>
-      <c r="M23" t="n">
-        <v>7</v>
-      </c>
-      <c r="N23" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH23" t="n">
-        <v>5.4</v>
+        <v>1.09</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.26</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>3.22</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.09</v>
+        <v>1.34</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.73</v>
+        <v>3.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.44</v>
+        <v>1.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.61</v>
+        <v>3.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.4</v>
+        <v>2.82</v>
       </c>
       <c r="M28" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="O28" t="n">
-        <v>5.45</v>
+        <v>3.15</v>
       </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="U28" t="n">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.86</v>
+        <v>1.17</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="N29" t="n">
-        <v>2.38</v>
+        <v>17.56</v>
       </c>
       <c r="O29" t="n">
-        <v>3.54</v>
+        <v>1.52</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.85</v>
+        <v>8.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="V29" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AB29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC29" t="n">
-        <v>2.69</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.48</v>
+        <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.43</v>
+        <v>5.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46001.70833333334</v>

--- a/jogos_2025-12-10.xlsx
+++ b/jogos_2025-12-10.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="N2" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P2" t="n">
         <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.62</v>
+        <v>6.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -683,13 +683,13 @@
         <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,34 +698,34 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG2" t="n">
         <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46001.375</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.03</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.77</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.95</v>
+        <v>3.84</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46001.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
-        <v>2.55</v>
+        <v>5.58</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>2.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.15</v>
+        <v>6.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.92</v>
+        <v>2.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.81</v>
+        <v>4.94</v>
       </c>
       <c r="R6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.4</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC6" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46001.41666666666</v>
@@ -1278,10 +1278,10 @@
         <v>2.04</v>
       </c>
       <c r="T7" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
         <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
         <v>1.02</v>
@@ -1317,7 +1317,7 @@
         <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
         <v>1.33</v>
@@ -1382,13 +1382,13 @@
         <v>5.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
@@ -1397,19 +1397,19 @@
         <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="U8" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
         <v>1.6</v>
@@ -1424,22 +1424,22 @@
         <v>1.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46001.44791666666</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
         <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46001.45833333334</v>
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.72</v>
+        <v>4.15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
         <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA10" t="n">
         <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
         <v>3.42</v>
@@ -1677,7 +1677,7 @@
         <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46001.5</v>
@@ -1733,19 +1733,19 @@
         <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="O11" t="n">
         <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -1769,34 +1769,34 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46001.58333333334</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="N12" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="O12" t="n">
         <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
@@ -1876,7 +1876,7 @@
         <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V12" t="n">
         <v>5.3</v>
@@ -1888,34 +1888,34 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AG12" t="n">
         <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46001.61458333334</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="P13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46001.61458333334</v>
@@ -2087,25 +2087,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.69</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
         <v>3.3</v>
@@ -2117,43 +2117,43 @@
         <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="W14" t="n">
         <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
         <v>1.47</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46001.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,19 +2206,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="O15" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
         <v>3.5</v>
@@ -2227,52 +2227,52 @@
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
         <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="N16" t="n">
-        <v>5.19</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.49</v>
+        <v>3.31</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>3.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>2.87</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.92</v>
+        <v>2.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.18</v>
+        <v>3.82</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>5.49</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.47</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.95</v>
+        <v>3.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>2.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="N19" t="n">
-        <v>5.27</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.28</v>
+        <v>3.11</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>6.85</v>
+        <v>8.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.99</v>
+        <v>3.92</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH19" t="n">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.02</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="R20" t="n">
         <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
         <v>8</v>
@@ -2840,34 +2840,34 @@
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG20" t="n">
         <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46001.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>7.58</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3161,70 +3161,70 @@
         <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O23" t="n">
-        <v>5.45</v>
+        <v>4.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46001.70833333334</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="M24" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="N24" t="n">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="O24" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v